--- a/output/pdf_financials_xlsx/MGA.xlsx
+++ b/output/pdf_financials_xlsx/MGA.xlsx
@@ -5455,31 +5455,31 @@
         <v>58.473</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>60.298</v>
+        <v>37.986</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>38.752</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>35.488</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>35.488</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>35.488</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>35.642</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.426</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.887</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -11797,7 +11797,11 @@
           <t>Warrant reserve (note 16)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12899,7 +12903,11 @@
           <t>Warrant reserve (note 18)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -16416,7 +16424,11 @@
           <t>Warrant reserve 16</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -17749,7 +17761,11 @@
           <t>Warrant reserve 14</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -18663,7 +18679,11 @@
           <t>Warrant reserve 15</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -19917,7 +19937,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MGA.xlsx
+++ b/output/pdf_financials_xlsx/MGA.xlsx
@@ -1001,25 +1001,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.824</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.914</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1913,25 +1913,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-16.328</v>
+        <v>-17.152</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-46.982</v>
+        <v>-48.422</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-126.4</v>
+        <v>-127.314</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-23.889</v>
+        <v>-24.555</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-77.871</v>
+        <v>-78</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-11.858</v>
+        <v>-11.882</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-8.882</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2025,25 +2025,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-16.328</v>
+        <v>-17.152</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-46.982</v>
+        <v>-48.422</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-126.4</v>
+        <v>-127.314</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-23.889</v>
+        <v>-24.555</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-77.871</v>
+        <v>-78</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-11.858</v>
+        <v>-11.882</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-8.882</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -45566,7 +45566,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E417" s="5" t="n">

--- a/output/pdf_financials_xlsx/MGA.xlsx
+++ b/output/pdf_financials_xlsx/MGA.xlsx
@@ -4265,22 +4265,22 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="71">
@@ -4317,22 +4317,22 @@
         <v>0</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="72">
@@ -4525,22 +4525,22 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.969</v>
+        <v>0.888</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>1.106</v>
+        <v>1.05</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2.452</v>
+        <v>2.389</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>10.087</v>
+        <v>10.005</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>16.83</v>
+        <v>16.74</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>19.71</v>
+        <v>19.61</v>
       </c>
     </row>
     <row r="76">
@@ -4821,24 +4821,22 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.002311487510197739</v>
+        <v>0.003884852958315528</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.0004604051565377532</v>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0008696541845713117</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.0005457475008229526</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.001946296009231988</v>
+        <v>0.002417081474591938</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.001376291309466563</v>
+        <v>0.0018737459996352</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.000617736926986812</v>
+        <v>0.001032325468588699</v>
       </c>
     </row>
     <row r="81">
@@ -6745,10 +6743,10 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-23.98</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-36.391</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>-8.089</v>
@@ -6757,19 +6755,19 @@
         <v>-0.209</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-0.174</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.204</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="K114" s="1" t="inlineStr">
         <is>
@@ -6809,31 +6807,31 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>51.468</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>9.365</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>25.12</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>14.166</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>9.489000000000001</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>2.184</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="K115" s="1" t="inlineStr">
         <is>
@@ -9357,7 +9355,11 @@
           <t>Lease liabilities (note 12)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10828,7 +10830,11 @@
           <t>Lease liabilities (note 13)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -22305,7 +22311,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -23035,7 +23045,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -23124,7 +23138,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -27333,7 +27351,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -27422,7 +27444,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -28781,7 +28807,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -28870,7 +28900,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -30767,7 +30801,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -32941,7 +32979,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -34474,7 +34516,11 @@
           <t>Amortization of premium on purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E293" s="5" t="n">
         <v>0.585</v>
       </c>
@@ -35188,7 +35234,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E301" s="5" t="n">
         <v>51.468</v>
       </c>
@@ -35277,7 +35327,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E302" s="5" t="n">
         <v>-23.98</v>
       </c>
